--- a/feedback_forms/040_rule_suggestions_submission_form--feedback_forms.xlsx
+++ b/feedback_forms/040_rule_suggestions_submission_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>submit_rule_suggestion</t>
+          <t>rule_suggestion_submit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>suggestion_description</t>
+          <t>rule_suggestion_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,12 +561,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>suggestion_category</t>
+          <t>submitter_category</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>suggested_by</t>
+          <t>submitter_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Suggested By</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>submitter_department</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submitter_department</t>
+          <t>submitter_position</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submitter_position</t>
+          <t>submitter_comment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,35 +704,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submitter_comment</t>
+          <t>submitter_attachment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Attachment</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submitter_attachment</t>
+          <t>submitter_notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Attachment</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submitter_notes</t>
+          <t>submit_form_submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submit_rule_suggestion_submit</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit (2)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submit_form_submit</t>
+          <t>submitter_email_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submitter Email 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submitter_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submitter_attachment_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submitter Attachment 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submit_form</t>
+          <t>submitter_position_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submitter Position 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,200 +888,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>submitter_department_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Submitter Department 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submitter_phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitter_department</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submitter_position</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submitter_comment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submitter_attachment</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Attachment</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitter_notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_form</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +942,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submit_rule_suggestion_choices</t>
+          <t>rule_suggestion_submit_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>submit_rule_suggestion_choices</t>
+          <t>rule_suggestion_submit_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>suggestion_category_choices</t>
+          <t>submitter_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>suggestion_category_choices</t>
+          <t>submitter_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Category 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>submitter_category_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>category_3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
